--- a/assets/binomial/Binomial Option Pricing - Three Period American.xlsx
+++ b/assets/binomial/Binomial Option Pricing - Three Period American.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\FIN 203\FIN 203 Fall 2018\5 Binomial\new fall 2018\probability\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\FIN 203\FIN 203 Fall 2020\5 Binomial\2 Exercises\new fall 2018\new hw 2 three period american\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF3976E-EB5A-491C-B572-BBCB2F5AECFB}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1D7390-1921-43E1-BF18-8FF1EB025BB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20010" windowHeight="9570" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16512" yWindow="-96" windowWidth="16608" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Binomial Option Pricing Model" sheetId="19" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <definedName name="solvero_CPop" hidden="1">"System.Boolean:False"</definedName>
     <definedName name="solvero_CTyp" hidden="1">"RiskSolver.Globals.ChartType:Bar"</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +49,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -57,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>u</t>
   </si>
@@ -100,6 +103,75 @@
   <si>
     <t>Strike price</t>
   </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>C0</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Suuu</t>
+  </si>
+  <si>
+    <t>Suud</t>
+  </si>
+  <si>
+    <t>Sudu</t>
+  </si>
+  <si>
+    <t>Sudd</t>
+  </si>
+  <si>
+    <t>Sduu</t>
+  </si>
+  <si>
+    <t>Sdud</t>
+  </si>
+  <si>
+    <t>Sddu</t>
+  </si>
+  <si>
+    <t>Sddd</t>
+  </si>
+  <si>
+    <t>Cuuu</t>
+  </si>
+  <si>
+    <t>Cuud</t>
+  </si>
+  <si>
+    <t>Cudu</t>
+  </si>
+  <si>
+    <t>Cudd</t>
+  </si>
+  <si>
+    <t>Cduu</t>
+  </si>
+  <si>
+    <t>Cdud</t>
+  </si>
+  <si>
+    <t>Cddu</t>
+  </si>
+  <si>
+    <t>Cddd</t>
+  </si>
 </sst>
 </file>
 
@@ -127,12 +199,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -149,7 +227,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -160,6 +238,21 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -477,24 +570,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63CA6DFC-F54A-469D-89F7-17255BAED35A}">
   <dimension ref="A1:APZ103"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.9375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.4375" customWidth="1"/>
-    <col min="5" max="7" width="7.3125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.4375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.4375" customWidth="1"/>
-    <col min="10" max="10" width="4.8125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.4375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="6.1875" bestFit="1" customWidth="1"/>
-    <col min="14" max="98" width="6.4375" bestFit="1" customWidth="1"/>
-    <col min="99" max="998" width="7.4375" bestFit="1" customWidth="1"/>
-    <col min="999" max="999" width="8.4375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.4140625" customWidth="1"/>
+    <col min="5" max="7" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.4140625" customWidth="1"/>
+    <col min="10" max="10" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="98" width="6.4140625" bestFit="1" customWidth="1"/>
+    <col min="99" max="998" width="7.4140625" bestFit="1" customWidth="1"/>
+    <col min="999" max="999" width="8.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -504,8 +597,20 @@
       <c r="C1" s="2">
         <v>1.1000000000000001</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -514,6 +619,10 @@
       </c>
       <c r="C2" s="2">
         <v>0.8</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" t="s">
+        <v>21</v>
       </c>
       <c r="ALL2" s="3"/>
       <c r="ALM2" s="3"/>
@@ -635,7 +744,8 @@
       <c r="APY2" s="3"/>
       <c r="APZ2" s="3"/>
     </row>
-    <row r="3" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="G3" s="13"/>
       <c r="ALL3" s="3"/>
       <c r="ALM3" s="3"/>
       <c r="ALN3" s="3"/>
@@ -756,7 +866,7 @@
       <c r="APY3" s="3"/>
       <c r="APZ3" s="3"/>
     </row>
-    <row r="4" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -765,6 +875,11 @@
       </c>
       <c r="C4" s="2">
         <v>0.55000000000000004</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="H4" s="12"/>
+      <c r="I4" t="s">
+        <v>22</v>
       </c>
       <c r="ALL4" s="3"/>
       <c r="ALM4" s="3"/>
@@ -886,7 +1001,7 @@
       <c r="APY4" s="3"/>
       <c r="APZ4" s="3"/>
     </row>
-    <row r="5" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -897,6 +1012,7 @@
         <f>1-C4</f>
         <v>0.44999999999999996</v>
       </c>
+      <c r="F5" s="13"/>
       <c r="ALL5" s="3"/>
       <c r="ALM5" s="3"/>
       <c r="ALN5" s="3"/>
@@ -1017,7 +1133,12 @@
       <c r="APY5" s="3"/>
       <c r="APZ5" s="3"/>
     </row>
-    <row r="6" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="E6" s="14"/>
+      <c r="H6" s="12"/>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
       <c r="ALL6" s="3"/>
       <c r="ALM6" s="3"/>
       <c r="ALN6" s="3"/>
@@ -1138,7 +1259,7 @@
       <c r="APY6" s="3"/>
       <c r="APZ6" s="3"/>
     </row>
-    <row r="7" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
@@ -1148,6 +1269,8 @@
       <c r="C7" s="8">
         <v>50</v>
       </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="13"/>
       <c r="ALL7" s="3"/>
       <c r="ALM7" s="3"/>
       <c r="ALN7" s="3"/>
@@ -1268,7 +1391,7 @@
       <c r="APY7" s="3"/>
       <c r="APZ7" s="3"/>
     </row>
-    <row r="8" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1277,6 +1400,11 @@
       </c>
       <c r="C8" s="9">
         <v>44</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="H8" s="12"/>
+      <c r="I8" t="s">
+        <v>24</v>
       </c>
       <c r="ALL8" s="3"/>
       <c r="ALM8" s="3"/>
@@ -1398,7 +1526,7 @@
       <c r="APY8" s="3"/>
       <c r="APZ8" s="3"/>
     </row>
-    <row r="9" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1408,6 +1536,7 @@
       <c r="C9" s="7">
         <v>2.5000000000000001E-2</v>
       </c>
+      <c r="E9" s="13"/>
       <c r="ALL9" s="3"/>
       <c r="ALM9" s="3"/>
       <c r="ALN9" s="3"/>
@@ -1528,8 +1657,13 @@
       <c r="APY9" s="3"/>
       <c r="APZ9" s="3"/>
     </row>
-    <row r="10" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="C10" s="4"/>
+      <c r="E10" s="14"/>
+      <c r="H10" s="12"/>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
       <c r="ALL10" s="3"/>
       <c r="ALM10" s="3"/>
       <c r="ALN10" s="3"/>
@@ -1650,7 +1784,8 @@
       <c r="APY10" s="3"/>
       <c r="APZ10" s="3"/>
     </row>
-    <row r="11" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="G11" s="13"/>
       <c r="ALL11" s="3"/>
       <c r="ALM11" s="3"/>
       <c r="ALN11" s="3"/>
@@ -1771,7 +1906,11 @@
       <c r="APY11" s="3"/>
       <c r="APZ11" s="3"/>
     </row>
-    <row r="12" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="H12" s="12"/>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
       <c r="ALL12" s="3"/>
       <c r="ALM12" s="3"/>
       <c r="ALN12" s="3"/>
@@ -1892,8 +2031,9 @@
       <c r="APY12" s="3"/>
       <c r="APZ12" s="3"/>
     </row>
-    <row r="13" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="C13" s="2"/>
+      <c r="F13" s="13"/>
       <c r="ALL13" s="3"/>
       <c r="ALM13" s="3"/>
       <c r="ALN13" s="3"/>
@@ -2014,7 +2154,12 @@
       <c r="APY13" s="3"/>
       <c r="APZ13" s="3"/>
     </row>
-    <row r="14" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="F14" s="14"/>
+      <c r="H14" s="12"/>
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
       <c r="ALL14" s="3"/>
       <c r="ALM14" s="3"/>
       <c r="ALN14" s="3"/>
@@ -2135,8 +2280,9 @@
       <c r="APY14" s="3"/>
       <c r="APZ14" s="3"/>
     </row>
-    <row r="15" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:1118" x14ac:dyDescent="0.35">
       <c r="C15" s="7"/>
+      <c r="G15" s="13"/>
       <c r="ALL15" s="3"/>
       <c r="ALM15" s="3"/>
       <c r="ALN15" s="3"/>
@@ -2257,7 +2403,11 @@
       <c r="APY15" s="3"/>
       <c r="APZ15" s="3"/>
     </row>
-    <row r="16" spans="1:1118" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:1118" x14ac:dyDescent="0.35">
+      <c r="H16" s="12"/>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
       <c r="ALL16" s="3"/>
       <c r="ALM16" s="3"/>
       <c r="ALN16" s="3"/>
@@ -2378,7 +2528,7 @@
       <c r="APY16" s="3"/>
       <c r="APZ16" s="3"/>
     </row>
-    <row r="17" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="17" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C17" s="2"/>
       <c r="ALL17" s="3"/>
       <c r="ALM17" s="3"/>
@@ -2500,7 +2650,7 @@
       <c r="APY17" s="3"/>
       <c r="APZ17" s="3"/>
     </row>
-    <row r="18" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="18" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="ALL18" s="3"/>
       <c r="ALM18" s="3"/>
       <c r="ALN18" s="3"/>
@@ -2621,7 +2771,19 @@
       <c r="APY18" s="3"/>
       <c r="APZ18" s="3"/>
     </row>
-    <row r="19" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="19" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E19" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="ALL19" s="3"/>
       <c r="ALM19" s="3"/>
       <c r="ALN19" s="3"/>
@@ -2742,8 +2904,12 @@
       <c r="APY19" s="3"/>
       <c r="APZ19" s="3"/>
     </row>
-    <row r="20" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="20" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C20" s="3"/>
+      <c r="H20" s="12"/>
+      <c r="I20" t="s">
+        <v>29</v>
+      </c>
       <c r="ALL20" s="3"/>
       <c r="ALM20" s="3"/>
       <c r="ALN20" s="3"/>
@@ -2864,8 +3030,9 @@
       <c r="APY20" s="3"/>
       <c r="APZ20" s="3"/>
     </row>
-    <row r="21" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="21" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C21" s="2"/>
+      <c r="G21" s="13"/>
       <c r="ALL21" s="3"/>
       <c r="ALM21" s="3"/>
       <c r="ALN21" s="3"/>
@@ -2986,7 +3153,8 @@
       <c r="APY21" s="3"/>
       <c r="APZ21" s="3"/>
     </row>
-    <row r="22" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="22" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="G22" s="16"/>
       <c r="ALL22" s="3"/>
       <c r="ALM22" s="3"/>
       <c r="ALN22" s="3"/>
@@ -3107,8 +3275,13 @@
       <c r="APY22" s="3"/>
       <c r="APZ22" s="3"/>
     </row>
-    <row r="23" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="23" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C23" s="1"/>
+      <c r="G23"/>
+      <c r="H23" s="12"/>
+      <c r="I23" t="s">
+        <v>30</v>
+      </c>
       <c r="ALL23" s="3"/>
       <c r="ALM23" s="3"/>
       <c r="ALN23" s="3"/>
@@ -3229,8 +3402,10 @@
       <c r="APY23" s="3"/>
       <c r="APZ23" s="3"/>
     </row>
-    <row r="24" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="24" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C24" s="1"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="13"/>
       <c r="ALL24" s="3"/>
       <c r="ALM24" s="3"/>
       <c r="ALN24" s="3"/>
@@ -3351,7 +3526,9 @@
       <c r="APY24" s="3"/>
       <c r="APZ24" s="3"/>
     </row>
-    <row r="25" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="25" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E25" s="14"/>
+      <c r="F25" s="16"/>
       <c r="ALL25" s="3"/>
       <c r="ALM25" s="3"/>
       <c r="ALN25" s="3"/>
@@ -3472,8 +3649,14 @@
       <c r="APY25" s="3"/>
       <c r="APZ25" s="3"/>
     </row>
-    <row r="26" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="26" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C26" s="4"/>
+      <c r="E26" s="14"/>
+      <c r="F26"/>
+      <c r="H26" s="12"/>
+      <c r="I26" t="s">
+        <v>31</v>
+      </c>
       <c r="ALL26" s="3"/>
       <c r="ALM26" s="3"/>
       <c r="ALN26" s="3"/>
@@ -3594,8 +3777,11 @@
       <c r="APY26" s="3"/>
       <c r="APZ26" s="3"/>
     </row>
-    <row r="27" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="27" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C27" s="4"/>
+      <c r="E27"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="16"/>
       <c r="ALL27" s="3"/>
       <c r="ALM27" s="3"/>
       <c r="ALN27" s="3"/>
@@ -3716,8 +3902,11 @@
       <c r="APY27" s="3"/>
       <c r="APZ27" s="3"/>
     </row>
-    <row r="28" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="28" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C28" s="4"/>
+      <c r="E28"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="16"/>
       <c r="ALL28" s="3"/>
       <c r="ALM28" s="3"/>
       <c r="ALN28" s="3"/>
@@ -3838,7 +4027,14 @@
       <c r="APY28" s="3"/>
       <c r="APZ28" s="3"/>
     </row>
-    <row r="29" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="29" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E29" s="14"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29" s="16"/>
+      <c r="I29" t="s">
+        <v>32</v>
+      </c>
       <c r="ALL29" s="3"/>
       <c r="ALM29" s="3"/>
       <c r="ALN29" s="3"/>
@@ -3959,8 +4155,10 @@
       <c r="APY29" s="3"/>
       <c r="APZ29" s="3"/>
     </row>
-    <row r="30" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="30" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C30" s="5"/>
+      <c r="E30" s="13"/>
+      <c r="F30"/>
       <c r="ALL30" s="3"/>
       <c r="ALM30" s="3"/>
       <c r="ALN30" s="3"/>
@@ -4081,8 +4279,12 @@
       <c r="APY30" s="3"/>
       <c r="APZ30" s="3"/>
     </row>
-    <row r="31" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="31" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C31" s="5"/>
+      <c r="H31" s="12"/>
+      <c r="I31" t="s">
+        <v>33</v>
+      </c>
       <c r="ALL31" s="3"/>
       <c r="ALM31" s="3"/>
       <c r="ALN31" s="3"/>
@@ -4203,7 +4405,8 @@
       <c r="APY31" s="3"/>
       <c r="APZ31" s="3"/>
     </row>
-    <row r="32" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="32" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="G32" s="13"/>
       <c r="ALL32" s="3"/>
       <c r="ALM32" s="3"/>
       <c r="ALN32" s="3"/>
@@ -4324,8 +4527,9 @@
       <c r="APY32" s="3"/>
       <c r="APZ32" s="3"/>
     </row>
-    <row r="33" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="33" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
+      <c r="G33" s="16"/>
       <c r="ALL33" s="3"/>
       <c r="ALM33" s="3"/>
       <c r="ALN33" s="3"/>
@@ -4446,7 +4650,12 @@
       <c r="APY33" s="3"/>
       <c r="APZ33" s="3"/>
     </row>
-    <row r="34" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="34" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="G34"/>
+      <c r="H34" s="12"/>
+      <c r="I34" t="s">
+        <v>34</v>
+      </c>
       <c r="ALL34" s="3"/>
       <c r="ALM34" s="3"/>
       <c r="ALN34" s="3"/>
@@ -4567,8 +4776,9 @@
       <c r="APY34" s="3"/>
       <c r="APZ34" s="3"/>
     </row>
-    <row r="35" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="35" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C35" s="4"/>
+      <c r="F35" s="13"/>
       <c r="ALL35" s="3"/>
       <c r="ALM35" s="3"/>
       <c r="ALN35" s="3"/>
@@ -4689,7 +4899,8 @@
       <c r="APY35" s="3"/>
       <c r="APZ35" s="3"/>
     </row>
-    <row r="36" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="36" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="F36" s="16"/>
       <c r="ALL36" s="3"/>
       <c r="ALM36" s="3"/>
       <c r="ALN36" s="3"/>
@@ -4810,8 +5021,13 @@
       <c r="APY36" s="3"/>
       <c r="APZ36" s="3"/>
     </row>
-    <row r="37" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="37" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C37" s="2"/>
+      <c r="F37"/>
+      <c r="H37" s="12"/>
+      <c r="I37" t="s">
+        <v>35</v>
+      </c>
       <c r="ALL37" s="3"/>
       <c r="ALM37" s="3"/>
       <c r="ALN37" s="3"/>
@@ -4932,8 +5148,10 @@
       <c r="APY37" s="3"/>
       <c r="APZ37" s="3"/>
     </row>
-    <row r="38" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="38" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C38" s="2"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="16"/>
       <c r="ALL38" s="3"/>
       <c r="ALM38" s="3"/>
       <c r="ALN38" s="3"/>
@@ -5054,7 +5272,9 @@
       <c r="APY38" s="3"/>
       <c r="APZ38" s="3"/>
     </row>
-    <row r="39" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="39" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="F39" s="14"/>
+      <c r="G39" s="16"/>
       <c r="ALL39" s="3"/>
       <c r="ALM39" s="3"/>
       <c r="ALN39" s="3"/>
@@ -5175,8 +5395,14 @@
       <c r="APY39" s="3"/>
       <c r="APZ39" s="3"/>
     </row>
-    <row r="40" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="40" spans="3:1118" x14ac:dyDescent="0.35">
       <c r="C40" s="6"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40" s="16"/>
+      <c r="I40" t="s">
+        <v>36</v>
+      </c>
       <c r="ALL40" s="3"/>
       <c r="ALM40" s="3"/>
       <c r="ALN40" s="3"/>
@@ -5297,7 +5523,11 @@
       <c r="APY40" s="3"/>
       <c r="APZ40" s="3"/>
     </row>
-    <row r="41" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="41" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
       <c r="ALL41" s="3"/>
       <c r="ALM41" s="3"/>
       <c r="ALN41" s="3"/>
@@ -5418,7 +5648,11 @@
       <c r="APY41" s="3"/>
       <c r="APZ41" s="3"/>
     </row>
-    <row r="42" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="42" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
       <c r="ALL42" s="3"/>
       <c r="ALM42" s="3"/>
       <c r="ALN42" s="3"/>
@@ -5539,7 +5773,11 @@
       <c r="APY42" s="3"/>
       <c r="APZ42" s="3"/>
     </row>
-    <row r="43" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="43" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
       <c r="ALL43" s="3"/>
       <c r="ALM43" s="3"/>
       <c r="ALN43" s="3"/>
@@ -5660,7 +5898,11 @@
       <c r="APY43" s="3"/>
       <c r="APZ43" s="3"/>
     </row>
-    <row r="44" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="44" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
       <c r="ALL44" s="3"/>
       <c r="ALM44" s="3"/>
       <c r="ALN44" s="3"/>
@@ -5781,7 +6023,11 @@
       <c r="APY44" s="3"/>
       <c r="APZ44" s="3"/>
     </row>
-    <row r="45" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="45" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
       <c r="ALL45" s="3"/>
       <c r="ALM45" s="3"/>
       <c r="ALN45" s="3"/>
@@ -5902,7 +6148,11 @@
       <c r="APY45" s="3"/>
       <c r="APZ45" s="3"/>
     </row>
-    <row r="46" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="46" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
       <c r="ALL46" s="3"/>
       <c r="ALM46" s="3"/>
       <c r="ALN46" s="3"/>
@@ -6023,7 +6273,11 @@
       <c r="APY46" s="3"/>
       <c r="APZ46" s="3"/>
     </row>
-    <row r="47" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="47" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
       <c r="ALL47" s="3"/>
       <c r="ALM47" s="3"/>
       <c r="ALN47" s="3"/>
@@ -6144,7 +6398,11 @@
       <c r="APY47" s="3"/>
       <c r="APZ47" s="3"/>
     </row>
-    <row r="48" spans="3:1118" x14ac:dyDescent="0.5">
+    <row r="48" spans="3:1118" x14ac:dyDescent="0.35">
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
       <c r="ALL48" s="3"/>
       <c r="ALM48" s="3"/>
       <c r="ALN48" s="3"/>
@@ -6265,7 +6523,11 @@
       <c r="APY48" s="3"/>
       <c r="APZ48" s="3"/>
     </row>
-    <row r="49" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="49" spans="5:1118" x14ac:dyDescent="0.35">
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
       <c r="ALL49" s="3"/>
       <c r="ALM49" s="3"/>
       <c r="ALN49" s="3"/>
@@ -6386,7 +6648,11 @@
       <c r="APY49" s="3"/>
       <c r="APZ49" s="3"/>
     </row>
-    <row r="50" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="50" spans="5:1118" x14ac:dyDescent="0.35">
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
       <c r="ALL50" s="3"/>
       <c r="ALM50" s="3"/>
       <c r="ALN50" s="3"/>
@@ -6507,7 +6773,11 @@
       <c r="APY50" s="3"/>
       <c r="APZ50" s="3"/>
     </row>
-    <row r="51" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="51" spans="5:1118" x14ac:dyDescent="0.35">
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
       <c r="ALL51" s="3"/>
       <c r="ALM51" s="3"/>
       <c r="ALN51" s="3"/>
@@ -6628,7 +6898,8 @@
       <c r="APY51" s="3"/>
       <c r="APZ51" s="3"/>
     </row>
-    <row r="52" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="52" spans="5:1118" x14ac:dyDescent="0.35">
+      <c r="F52"/>
       <c r="ALL52" s="3"/>
       <c r="ALM52" s="3"/>
       <c r="ALN52" s="3"/>
@@ -6749,7 +7020,7 @@
       <c r="APY52" s="3"/>
       <c r="APZ52" s="3"/>
     </row>
-    <row r="53" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="53" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL53" s="3"/>
       <c r="ALM53" s="3"/>
       <c r="ALN53" s="3"/>
@@ -6870,7 +7141,7 @@
       <c r="APY53" s="3"/>
       <c r="APZ53" s="3"/>
     </row>
-    <row r="54" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="54" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL54" s="3"/>
       <c r="ALM54" s="3"/>
       <c r="ALN54" s="3"/>
@@ -6991,7 +7262,7 @@
       <c r="APY54" s="3"/>
       <c r="APZ54" s="3"/>
     </row>
-    <row r="55" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="55" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL55" s="3"/>
       <c r="ALM55" s="3"/>
       <c r="ALN55" s="3"/>
@@ -7112,7 +7383,7 @@
       <c r="APY55" s="3"/>
       <c r="APZ55" s="3"/>
     </row>
-    <row r="56" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="56" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL56" s="3"/>
       <c r="ALM56" s="3"/>
       <c r="ALN56" s="3"/>
@@ -7233,7 +7504,7 @@
       <c r="APY56" s="3"/>
       <c r="APZ56" s="3"/>
     </row>
-    <row r="57" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="57" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL57" s="3"/>
       <c r="ALM57" s="3"/>
       <c r="ALN57" s="3"/>
@@ -7354,7 +7625,7 @@
       <c r="APY57" s="3"/>
       <c r="APZ57" s="3"/>
     </row>
-    <row r="58" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="58" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL58" s="3"/>
       <c r="ALM58" s="3"/>
       <c r="ALN58" s="3"/>
@@ -7475,7 +7746,7 @@
       <c r="APY58" s="3"/>
       <c r="APZ58" s="3"/>
     </row>
-    <row r="59" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="59" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL59" s="3"/>
       <c r="ALM59" s="3"/>
       <c r="ALN59" s="3"/>
@@ -7596,7 +7867,7 @@
       <c r="APY59" s="3"/>
       <c r="APZ59" s="3"/>
     </row>
-    <row r="60" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="60" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL60" s="3"/>
       <c r="ALM60" s="3"/>
       <c r="ALN60" s="3"/>
@@ -7717,7 +7988,7 @@
       <c r="APY60" s="3"/>
       <c r="APZ60" s="3"/>
     </row>
-    <row r="61" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="61" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL61" s="3"/>
       <c r="ALM61" s="3"/>
       <c r="ALN61" s="3"/>
@@ -7838,7 +8109,7 @@
       <c r="APY61" s="3"/>
       <c r="APZ61" s="3"/>
     </row>
-    <row r="62" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="62" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL62" s="3"/>
       <c r="ALM62" s="3"/>
       <c r="ALN62" s="3"/>
@@ -7959,7 +8230,7 @@
       <c r="APY62" s="3"/>
       <c r="APZ62" s="3"/>
     </row>
-    <row r="63" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="63" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL63" s="3"/>
       <c r="ALM63" s="3"/>
       <c r="ALN63" s="3"/>
@@ -8080,7 +8351,7 @@
       <c r="APY63" s="3"/>
       <c r="APZ63" s="3"/>
     </row>
-    <row r="64" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="64" spans="5:1118" x14ac:dyDescent="0.35">
       <c r="ALL64" s="3"/>
       <c r="ALM64" s="3"/>
       <c r="ALN64" s="3"/>
@@ -8201,7 +8472,7 @@
       <c r="APY64" s="3"/>
       <c r="APZ64" s="3"/>
     </row>
-    <row r="65" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="65" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL65" s="3"/>
       <c r="ALM65" s="3"/>
       <c r="ALN65" s="3"/>
@@ -8322,7 +8593,7 @@
       <c r="APY65" s="3"/>
       <c r="APZ65" s="3"/>
     </row>
-    <row r="66" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="66" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL66" s="3"/>
       <c r="ALM66" s="3"/>
       <c r="ALN66" s="3"/>
@@ -8443,7 +8714,7 @@
       <c r="APY66" s="3"/>
       <c r="APZ66" s="3"/>
     </row>
-    <row r="67" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="67" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL67" s="3"/>
       <c r="ALM67" s="3"/>
       <c r="ALN67" s="3"/>
@@ -8564,7 +8835,7 @@
       <c r="APY67" s="3"/>
       <c r="APZ67" s="3"/>
     </row>
-    <row r="68" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="68" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL68" s="3"/>
       <c r="ALM68" s="3"/>
       <c r="ALN68" s="3"/>
@@ -8685,7 +8956,7 @@
       <c r="APY68" s="3"/>
       <c r="APZ68" s="3"/>
     </row>
-    <row r="69" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="69" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL69" s="3"/>
       <c r="ALM69" s="3"/>
       <c r="ALN69" s="3"/>
@@ -8806,7 +9077,7 @@
       <c r="APY69" s="3"/>
       <c r="APZ69" s="3"/>
     </row>
-    <row r="70" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="70" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL70" s="3"/>
       <c r="ALM70" s="3"/>
       <c r="ALN70" s="3"/>
@@ -8927,7 +9198,7 @@
       <c r="APY70" s="3"/>
       <c r="APZ70" s="3"/>
     </row>
-    <row r="71" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="71" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL71" s="3"/>
       <c r="ALM71" s="3"/>
       <c r="ALN71" s="3"/>
@@ -9048,7 +9319,7 @@
       <c r="APY71" s="3"/>
       <c r="APZ71" s="3"/>
     </row>
-    <row r="72" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="72" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL72" s="3"/>
       <c r="ALM72" s="3"/>
       <c r="ALN72" s="3"/>
@@ -9169,7 +9440,7 @@
       <c r="APY72" s="3"/>
       <c r="APZ72" s="3"/>
     </row>
-    <row r="73" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="73" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL73" s="3"/>
       <c r="ALM73" s="3"/>
       <c r="ALN73" s="3"/>
@@ -9290,7 +9561,7 @@
       <c r="APY73" s="3"/>
       <c r="APZ73" s="3"/>
     </row>
-    <row r="74" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="74" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL74" s="3"/>
       <c r="ALM74" s="3"/>
       <c r="ALN74" s="3"/>
@@ -9411,7 +9682,7 @@
       <c r="APY74" s="3"/>
       <c r="APZ74" s="3"/>
     </row>
-    <row r="75" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="75" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL75" s="3"/>
       <c r="ALM75" s="3"/>
       <c r="ALN75" s="3"/>
@@ -9532,7 +9803,7 @@
       <c r="APY75" s="3"/>
       <c r="APZ75" s="3"/>
     </row>
-    <row r="76" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="76" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL76" s="3"/>
       <c r="ALM76" s="3"/>
       <c r="ALN76" s="3"/>
@@ -9653,7 +9924,7 @@
       <c r="APY76" s="3"/>
       <c r="APZ76" s="3"/>
     </row>
-    <row r="77" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="77" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL77" s="3"/>
       <c r="ALM77" s="3"/>
       <c r="ALN77" s="3"/>
@@ -9774,7 +10045,7 @@
       <c r="APY77" s="3"/>
       <c r="APZ77" s="3"/>
     </row>
-    <row r="78" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="78" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL78" s="3"/>
       <c r="ALM78" s="3"/>
       <c r="ALN78" s="3"/>
@@ -9895,7 +10166,7 @@
       <c r="APY78" s="3"/>
       <c r="APZ78" s="3"/>
     </row>
-    <row r="79" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="79" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL79" s="3"/>
       <c r="ALM79" s="3"/>
       <c r="ALN79" s="3"/>
@@ -10016,7 +10287,7 @@
       <c r="APY79" s="3"/>
       <c r="APZ79" s="3"/>
     </row>
-    <row r="80" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="80" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL80" s="3"/>
       <c r="ALM80" s="3"/>
       <c r="ALN80" s="3"/>
@@ -10137,7 +10408,7 @@
       <c r="APY80" s="3"/>
       <c r="APZ80" s="3"/>
     </row>
-    <row r="81" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="81" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL81" s="3"/>
       <c r="ALM81" s="3"/>
       <c r="ALN81" s="3"/>
@@ -10258,7 +10529,7 @@
       <c r="APY81" s="3"/>
       <c r="APZ81" s="3"/>
     </row>
-    <row r="82" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="82" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL82" s="3"/>
       <c r="ALM82" s="3"/>
       <c r="ALN82" s="3"/>
@@ -10379,7 +10650,7 @@
       <c r="APY82" s="3"/>
       <c r="APZ82" s="3"/>
     </row>
-    <row r="83" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="83" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL83" s="3"/>
       <c r="ALM83" s="3"/>
       <c r="ALN83" s="3"/>
@@ -10500,7 +10771,7 @@
       <c r="APY83" s="3"/>
       <c r="APZ83" s="3"/>
     </row>
-    <row r="84" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="84" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL84" s="3"/>
       <c r="ALM84" s="3"/>
       <c r="ALN84" s="3"/>
@@ -10621,7 +10892,7 @@
       <c r="APY84" s="3"/>
       <c r="APZ84" s="3"/>
     </row>
-    <row r="85" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="85" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL85" s="3"/>
       <c r="ALM85" s="3"/>
       <c r="ALN85" s="3"/>
@@ -10742,7 +11013,7 @@
       <c r="APY85" s="3"/>
       <c r="APZ85" s="3"/>
     </row>
-    <row r="86" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="86" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL86" s="3"/>
       <c r="ALM86" s="3"/>
       <c r="ALN86" s="3"/>
@@ -10863,7 +11134,7 @@
       <c r="APY86" s="3"/>
       <c r="APZ86" s="3"/>
     </row>
-    <row r="87" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="87" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL87" s="3"/>
       <c r="ALM87" s="3"/>
       <c r="ALN87" s="3"/>
@@ -10984,7 +11255,7 @@
       <c r="APY87" s="3"/>
       <c r="APZ87" s="3"/>
     </row>
-    <row r="88" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="88" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL88" s="3"/>
       <c r="ALM88" s="3"/>
       <c r="ALN88" s="3"/>
@@ -11105,7 +11376,7 @@
       <c r="APY88" s="3"/>
       <c r="APZ88" s="3"/>
     </row>
-    <row r="89" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="89" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL89" s="3"/>
       <c r="ALM89" s="3"/>
       <c r="ALN89" s="3"/>
@@ -11226,7 +11497,7 @@
       <c r="APY89" s="3"/>
       <c r="APZ89" s="3"/>
     </row>
-    <row r="90" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="90" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL90" s="3"/>
       <c r="ALM90" s="3"/>
       <c r="ALN90" s="3"/>
@@ -11347,7 +11618,7 @@
       <c r="APY90" s="3"/>
       <c r="APZ90" s="3"/>
     </row>
-    <row r="91" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="91" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL91" s="3"/>
       <c r="ALM91" s="3"/>
       <c r="ALN91" s="3"/>
@@ -11468,7 +11739,7 @@
       <c r="APY91" s="3"/>
       <c r="APZ91" s="3"/>
     </row>
-    <row r="92" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="92" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL92" s="3"/>
       <c r="ALM92" s="3"/>
       <c r="ALN92" s="3"/>
@@ -11589,7 +11860,7 @@
       <c r="APY92" s="3"/>
       <c r="APZ92" s="3"/>
     </row>
-    <row r="93" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="93" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL93" s="3"/>
       <c r="ALM93" s="3"/>
       <c r="ALN93" s="3"/>
@@ -11710,7 +11981,7 @@
       <c r="APY93" s="3"/>
       <c r="APZ93" s="3"/>
     </row>
-    <row r="94" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="94" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL94" s="3"/>
       <c r="ALM94" s="3"/>
       <c r="ALN94" s="3"/>
@@ -11831,7 +12102,7 @@
       <c r="APY94" s="3"/>
       <c r="APZ94" s="3"/>
     </row>
-    <row r="95" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="95" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL95" s="3"/>
       <c r="ALM95" s="3"/>
       <c r="ALN95" s="3"/>
@@ -11952,7 +12223,7 @@
       <c r="APY95" s="3"/>
       <c r="APZ95" s="3"/>
     </row>
-    <row r="96" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="96" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL96" s="3"/>
       <c r="ALM96" s="3"/>
       <c r="ALN96" s="3"/>
@@ -12073,7 +12344,7 @@
       <c r="APY96" s="3"/>
       <c r="APZ96" s="3"/>
     </row>
-    <row r="97" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="97" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL97" s="3"/>
       <c r="ALM97" s="3"/>
       <c r="ALN97" s="3"/>
@@ -12194,7 +12465,7 @@
       <c r="APY97" s="3"/>
       <c r="APZ97" s="3"/>
     </row>
-    <row r="98" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="98" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL98" s="3"/>
       <c r="ALM98" s="3"/>
       <c r="ALN98" s="3"/>
@@ -12315,7 +12586,7 @@
       <c r="APY98" s="3"/>
       <c r="APZ98" s="3"/>
     </row>
-    <row r="99" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="99" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL99" s="3"/>
       <c r="ALM99" s="3"/>
       <c r="ALN99" s="3"/>
@@ -12436,7 +12707,7 @@
       <c r="APY99" s="3"/>
       <c r="APZ99" s="3"/>
     </row>
-    <row r="100" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="100" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL100" s="3"/>
       <c r="ALM100" s="3"/>
       <c r="ALN100" s="3"/>
@@ -12557,7 +12828,7 @@
       <c r="APY100" s="3"/>
       <c r="APZ100" s="3"/>
     </row>
-    <row r="101" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="101" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL101" s="3"/>
       <c r="ALM101" s="3"/>
       <c r="ALN101" s="3"/>
@@ -12678,7 +12949,7 @@
       <c r="APY101" s="3"/>
       <c r="APZ101" s="3"/>
     </row>
-    <row r="102" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="102" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL102" s="3"/>
       <c r="ALM102" s="3"/>
       <c r="ALN102" s="3"/>
@@ -12799,7 +13070,7 @@
       <c r="APY102" s="3"/>
       <c r="APZ102" s="3"/>
     </row>
-    <row r="103" spans="1000:1118" x14ac:dyDescent="0.5">
+    <row r="103" spans="1000:1118" x14ac:dyDescent="0.35">
       <c r="ALL103" s="3"/>
       <c r="ALM103" s="3"/>
       <c r="ALN103" s="3"/>
